--- a/artfynd/A 28147-2022 artfynd.xlsx
+++ b/artfynd/A 28147-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127450154</v>
       </c>
       <c r="B2" t="n">
-        <v>57670</v>
+        <v>57674</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28147-2022 artfynd.xlsx
+++ b/artfynd/A 28147-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127450154</v>
       </c>
       <c r="B2" t="n">
-        <v>57674</v>
+        <v>57676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28147-2022 artfynd.xlsx
+++ b/artfynd/A 28147-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127450154</v>
       </c>
       <c r="B2" t="n">
-        <v>57676</v>
+        <v>57679</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28147-2022 artfynd.xlsx
+++ b/artfynd/A 28147-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127450154</v>
       </c>
       <c r="B2" t="n">
-        <v>57679</v>
+        <v>57685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28147-2022 artfynd.xlsx
+++ b/artfynd/A 28147-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127450154</v>
+        <v>127450357</v>
       </c>
       <c r="B2" t="n">
-        <v>57685</v>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,13 +708,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490962</v>
+        <v>490912</v>
       </c>
       <c r="R2" t="n">
-        <v>6569409</v>
+        <v>6569458</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,29 +759,45 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>08:38</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # grov, murken låga # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -791,6 +811,1679 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>62380893</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hopaskogen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>490913</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6569462</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hidinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2016-12-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2016-12-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>på läga av gran på marken</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Herbert Kaufmann</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Herbert Kaufmann</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127450360</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hopaskogen, Hällshyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>490912</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6569458</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hidinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # grov, murken låga # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127450388</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hopaskogen, Hällshyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>490920</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6569468</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hidinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Horizontal, dead with ground contact # grov, murken stamdel av granlåga # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127450351</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96458</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hopaskogen, Hällshyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>490912</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6569458</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hidinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Horizontal, dead with ground contact # grov, murken låga # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127450843</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96458</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hopaskogen, Hällshyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>490927</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6569488</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hidinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stump # grov murken stubbe</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127457133</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91087</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4823</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Hasselsopp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Leccinellum pseudoscabrum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Kallenb.) Mikšík</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hopaskogen, Hällshyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>490912</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6569458</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hidinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>under hassel</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Corylus avellana # under hassel</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127457148</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91087</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4823</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Hasselsopp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Leccinellum pseudoscabrum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Kallenb.) Mikšík</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hopaskogen, Hällshyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>490904</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6569455</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hidinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>hassel</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Corylus avellana</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>under hassel</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Corylus avellana # under hassel</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127450154</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57966</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hopaskogen, Hällshyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>490962</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6569409</v>
+      </c>
+      <c r="S10" t="n">
+        <v>75</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hidinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127450160</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58067</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100090</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nötkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nucifraga caryocatactes</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hopaskogen, Hällshyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>490979</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6569485</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hidinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127450392</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hopaskogen, Hällshyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>490920</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6569468</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hidinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127450830</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hopaskogen, Hällshyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>490927</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6569488</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hidinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127451071</v>
+      </c>
+      <c r="B14" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hopaskogen, Hällshyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>490904</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6569455</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hidinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127450378</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hopaskogen, Hällshyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>490912</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6569458</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hidinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127450394</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hopaskogen, Hällshyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>490920</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6569468</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hidinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
